--- a/data/trans_dic/P22$mutuaSPriv-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,65</t>
+          <t>2,85; 6,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,67</t>
+          <t>2,92; 7,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,06</t>
+          <t>4,53; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,29</t>
+          <t>4,68; 9,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,48</t>
+          <t>3,31; 8,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,65</t>
+          <t>3,29; 8,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,41</t>
+          <t>4,32; 9,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,34</t>
+          <t>5,98; 10,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,51</t>
+          <t>3,44; 6,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,15</t>
+          <t>3,67; 7,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,69</t>
+          <t>5,07; 8,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,96</t>
+          <t>5,85; 8,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,25</t>
+          <t>2,7; 8,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,99</t>
+          <t>4,83; 11,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,58</t>
+          <t>4,54; 10,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,7</t>
+          <t>4,9; 9,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,31</t>
+          <t>1,27; 4,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,32</t>
+          <t>4,08; 10,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,8</t>
+          <t>1,82; 5,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,76</t>
+          <t>3,12; 6,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,48</t>
+          <t>2,38; 5,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,6</t>
+          <t>5,09; 9,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,41</t>
+          <t>3,85; 7,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,78</t>
+          <t>4,46; 7,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,54</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,37</t>
+          <t>0,42; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,1</t>
+          <t>0,52; 5,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,61</t>
+          <t>0,77; 4,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,71</t>
+          <t>0,23; 2,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,92</t>
+          <t>0,39; 2,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,51</t>
+          <t>0,81; 2,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,51</t>
+          <t>0,18; 1,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,9</t>
+          <t>0,08; 0,92</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,07</t>
+          <t>0,73; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,99</t>
+          <t>0,16; 0,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,06</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,25</t>
+          <t>0,29; 1,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,37</t>
+          <t>0,57; 2,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,23</t>
+          <t>0,4; 2,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,36</t>
+          <t>0,15; 1,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,65</t>
+          <t>0,61; 2,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,89</t>
+          <t>0,84; 1,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,27</t>
+          <t>0,36; 1,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,89</t>
+          <t>0,21; 0,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,54</t>
+          <t>0,6; 1,59</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,53</t>
+          <t>0,56; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,76</t>
+          <t>0,19; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,68</t>
+          <t>0,17; 1,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,17</t>
+          <t>0,83; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,13; 1,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,96</t>
+          <t>0,19; 0,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,74</t>
+          <t>0,88; 2,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,98</t>
+          <t>0,14; 0,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,33</t>
+          <t>1,04; 4,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,49</t>
+          <t>1,08; 5,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,02</t>
+          <t>0,37; 3,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,94</t>
+          <t>2,32; 13,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,6</t>
+          <t>1,13; 2,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,65</t>
+          <t>0,29; 1,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,31</t>
+          <t>0,74; 2,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,46</t>
+          <t>0,97; 2,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,7</t>
+          <t>1,24; 2,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,02</t>
+          <t>0,63; 1,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,04</t>
+          <t>0,77; 2,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,49</t>
+          <t>1,61; 4,55</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,7</t>
+          <t>1,64; 2,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,82</t>
+          <t>1,71; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,63</t>
+          <t>1,64; 2,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,47</t>
+          <t>2,04; 3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,58</t>
+          <t>1,66; 2,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,44</t>
+          <t>1,4; 2,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,19</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,87</t>
+          <t>1,81; 2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,47</t>
+          <t>1,76; 2,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,43</t>
+          <t>1,68; 2,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,26</t>
+          <t>1,55; 2,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,98</t>
+          <t>2,08; 2,98</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13017; 31411</t>
+          <t>13483; 31047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12364; 33523</t>
+          <t>12759; 34288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20068; 43170</t>
+          <t>19445; 42487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24647; 46928</t>
+          <t>23637; 46395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10016; 26004</t>
+          <t>10157; 26218</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10139; 27188</t>
+          <t>10351; 27257</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15267; 32658</t>
+          <t>14990; 33971</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26126; 46264</t>
+          <t>26739; 46647</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27670; 50745</t>
+          <t>26772; 49800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27010; 53757</t>
+          <t>27567; 54782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39808; 67442</t>
+          <t>39353; 69656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54549; 85320</t>
+          <t>55779; 84615</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10255; 30277</t>
+          <t>9916; 29865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20987; 46034</t>
+          <t>20226; 46221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18127; 39797</t>
+          <t>17091; 39503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21633; 43854</t>
+          <t>22154; 44233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4150; 16036</t>
+          <t>4723; 17049</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13949; 34890</t>
+          <t>13796; 36510</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6761; 21588</t>
+          <t>6779; 21833</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11719; 25877</t>
+          <t>11928; 24996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17297; 40476</t>
+          <t>17586; 41212</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39082; 72630</t>
+          <t>38519; 73121</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29326; 55460</t>
+          <t>28856; 54165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37299; 64927</t>
+          <t>37235; 62632</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>860; 8316</t>
+          <t>858; 8064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2787; 14929</t>
+          <t>2646; 14863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6725</t>
+          <t>0; 5902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5532</t>
+          <t>0; 5444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>872; 8555</t>
+          <t>877; 9554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2034; 11990</t>
+          <t>2012; 12897</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8066</t>
+          <t>0; 7983</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>373; 4519</t>
+          <t>377; 4828</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2647; 13596</t>
+          <t>2776; 14400</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6677; 22371</t>
+          <t>7219; 23645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>960; 10406</t>
+          <t>1254; 10050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>696; 7502</t>
+          <t>665; 7655</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9080; 25544</t>
+          <t>8962; 24712</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1868; 11472</t>
+          <t>1901; 11333</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1125; 12120</t>
+          <t>1124; 12406</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2751; 12904</t>
+          <t>3048; 13421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3958; 16942</t>
+          <t>4078; 18877</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2975; 17066</t>
+          <t>3085; 17767</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1198; 11147</t>
+          <t>1196; 12685</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5969; 25921</t>
+          <t>5997; 24523</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16491; 36843</t>
+          <t>16342; 36330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7597; 24457</t>
+          <t>6858; 24142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4227; 17618</t>
+          <t>4094; 18395</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12515; 31078</t>
+          <t>12065; 32061</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1850; 12379</t>
+          <t>1950; 14319</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>983; 8963</t>
+          <t>969; 9129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1002; 9024</t>
+          <t>1001; 8539</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>807; 7981</t>
+          <t>793; 7796</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5028; 18028</t>
+          <t>4733; 18567</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>981; 8443</t>
+          <t>976; 8596</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 9030</t>
+          <t>0; 8503</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1377; 8055</t>
+          <t>1607; 7711</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8487; 25176</t>
+          <t>8080; 24845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2908; 13966</t>
+          <t>2932; 13962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1904; 13241</t>
+          <t>1919; 12740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3105; 12773</t>
+          <t>3184; 12770</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2769; 12873</t>
+          <t>3093; 13032</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2898; 14651</t>
+          <t>2881; 14613</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1055; 8659</t>
+          <t>1050; 8712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5502; 33517</t>
+          <t>5569; 32427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14007; 32355</t>
+          <t>14087; 33439</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3925; 18297</t>
+          <t>3204; 16998</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8143; 24982</t>
+          <t>8029; 25022</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7278; 18706</t>
+          <t>7389; 18817</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19582; 41730</t>
+          <t>19098; 40789</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8710; 27810</t>
+          <t>8612; 26629</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10209; 27852</t>
+          <t>10587; 29028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16163; 45029</t>
+          <t>16105; 45613</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>53200; 88130</t>
+          <t>53626; 87169</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58737; 96637</t>
+          <t>58372; 97334</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53948; 88899</t>
+          <t>55427; 89460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68374; 117040</t>
+          <t>69011; 117885</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54908; 86937</t>
+          <t>56197; 89994</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49815; 86621</t>
+          <t>49713; 87651</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46890; 77253</t>
+          <t>44825; 77164</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>66135; 102626</t>
+          <t>64888; 102988</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>117329; 164332</t>
+          <t>116618; 164141</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119555; 169177</t>
+          <t>117455; 169864</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109833; 156386</t>
+          <t>107352; 156182</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>143052; 207290</t>
+          <t>144682; 207213</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutuaSPriv-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,57</t>
+          <t>2,66; 6,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,84</t>
+          <t>2,79; 7,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,9</t>
+          <t>4,86; 10,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,18</t>
+          <t>4,65; 8,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,55</t>
+          <t>3,27; 8,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,67</t>
+          <t>3,27; 8,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,79</t>
+          <t>4,31; 9,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,42</t>
+          <t>6,05; 10,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,39</t>
+          <t>3,52; 6,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,29</t>
+          <t>3,6; 7,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,97</t>
+          <t>5,12; 9,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,88</t>
+          <t>5,92; 8,78</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,14</t>
+          <t>2,89; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,04</t>
+          <t>4,67; 10,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,5</t>
+          <t>4,81; 10,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,78</t>
+          <t>4,74; 9,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,58</t>
+          <t>1,12; 4,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,8</t>
+          <t>4,03; 10,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,86</t>
+          <t>1,81; 5,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,53</t>
+          <t>2,91; 6,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,58</t>
+          <t>2,33; 5,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,66</t>
+          <t>5,28; 9,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,24</t>
+          <t>3,76; 7,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,5</t>
+          <t>4,39; 7,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,49</t>
+          <t>0,16; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,36</t>
+          <t>0,44; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,15; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,69</t>
+          <t>0,52; 4,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,96</t>
+          <t>0,78; 4,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,89</t>
+          <t>0,2; 2,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,03</t>
+          <t>0,38; 1,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,66</t>
+          <t>0,86; 2,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,46</t>
+          <t>0,16; 1,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,92</t>
+          <t>0,26; 1,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,0</t>
+          <t>0,75; 2,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,98</t>
+          <t>0,24; 1,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,14; 1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,3</t>
+          <t>0,44; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,64</t>
+          <t>0,57; 2,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,32</t>
+          <t>0,39; 2,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,54</t>
+          <t>0,15; 1,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,51</t>
+          <t>0,97; 2,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,86</t>
+          <t>0,83; 1,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,25</t>
+          <t>0,36; 1,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,93</t>
+          <t>0,22; 0,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,59</t>
+          <t>0,8; 2,01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,08</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,79</t>
+          <t>0,19; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,38</t>
+          <t>0,16; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,64</t>
+          <t>0,14; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,26</t>
+          <t>0,79; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,13</t>
+          <t>0,13; 1,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,92</t>
+          <t>0,22; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,7</t>
+          <t>0,9; 2,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,1</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,94</t>
+          <t>0,14; 0,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,97</t>
+          <t>0,25; 0,96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,38</t>
+          <t>0,93; 4,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,48</t>
+          <t>1,09; 5,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,03</t>
+          <t>0,36; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,48</t>
+          <t>2,42; 15,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,68</t>
+          <t>1,15; 2,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,53</t>
+          <t>0,35; 1,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,32</t>
+          <t>0,72; 2,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,47</t>
+          <t>0,87; 2,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,64</t>
+          <t>1,26; 2,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,93</t>
+          <t>0,64; 1,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,12</t>
+          <t>0,74; 2,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,55</t>
+          <t>1,51; 4,26</t>
         </is>
       </c>
     </row>
@@ -1504,47 +1504,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,67</t>
+          <t>1,63; 2,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,85</t>
+          <t>1,72; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,64</t>
+          <t>1,59; 2,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,49</t>
+          <t>2,36; 3,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,67</t>
+          <t>1,61; 2,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,47</t>
+          <t>1,45; 2,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,3; 2,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,88</t>
+          <t>2,07; 2,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,47</t>
+          <t>1,79; 2,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,44</t>
+          <t>1,7; 2,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,26</t>
+          <t>1,54; 2,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 2,98</t>
+          <t>2,31; 3,12</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>74057</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13483; 31047</t>
+          <t>12571; 30279</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12759; 34288</t>
+          <t>12212; 33628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19445; 42487</t>
+          <t>20850; 43144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23637; 46395</t>
+          <t>25625; 48605</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10157; 26218</t>
+          <t>10028; 25406</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10351; 27257</t>
+          <t>10277; 27832</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14990; 33971</t>
+          <t>14966; 34364</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26739; 46647</t>
+          <t>29557; 50560</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26772; 49800</t>
+          <t>27414; 54138</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27567; 54782</t>
+          <t>27082; 54218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39353; 69656</t>
+          <t>39722; 70210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55779; 84615</t>
+          <t>61468; 91203</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49348</t>
+          <t>52508</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9916; 29865</t>
+          <t>10623; 29741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20226; 46221</t>
+          <t>19570; 44462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17091; 39503</t>
+          <t>18097; 38663</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22154; 44233</t>
+          <t>22913; 46591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4723; 17049</t>
+          <t>4182; 16249</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13796; 36510</t>
+          <t>13624; 35101</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6779; 21833</t>
+          <t>6747; 21139</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11928; 24996</t>
+          <t>12306; 26526</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17586; 41212</t>
+          <t>17245; 39952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38519; 73121</t>
+          <t>39963; 74166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28856; 54165</t>
+          <t>28127; 55101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37235; 62632</t>
+          <t>39808; 67769</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>4279</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>858; 8064</t>
+          <t>864; 8980</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2646; 14863</t>
+          <t>2754; 13523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 6441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5444</t>
+          <t>726; 7584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>877; 9554</t>
+          <t>869; 8307</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2012; 12897</t>
+          <t>2027; 12040</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7983</t>
+          <t>0; 8166</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>377; 4828</t>
+          <t>382; 4712</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2776; 14400</t>
+          <t>2661; 13279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7219; 23645</t>
+          <t>7663; 22543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1254; 10050</t>
+          <t>1078; 10551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>665; 7655</t>
+          <t>1737; 9526</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>25049</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8962; 24712</t>
+          <t>9257; 25861</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1901; 11333</t>
+          <t>2762; 12198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1124; 12406</t>
+          <t>1626; 11820</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3048; 13421</t>
+          <t>4958; 24859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4078; 18877</t>
+          <t>4089; 17526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3085; 17767</t>
+          <t>3010; 16767</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1196; 12685</t>
+          <t>1194; 11392</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5997; 24523</t>
+          <t>8371; 24386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16342; 36330</t>
+          <t>16238; 36967</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6858; 24142</t>
+          <t>6966; 24344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4094; 18395</t>
+          <t>4243; 17506</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12065; 32061</t>
+          <t>15917; 40064</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>7165</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1950; 14319</t>
+          <t>1847; 12454</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>969; 9129</t>
+          <t>982; 9245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1001; 8539</t>
+          <t>1013; 9147</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>793; 7796</t>
+          <t>779; 8542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4733; 18567</t>
+          <t>4511; 17412</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>976; 8596</t>
+          <t>977; 8010</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 8503</t>
+          <t>0; 9640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1607; 7711</t>
+          <t>1862; 8919</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8080; 24845</t>
+          <t>8273; 26245</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2932; 13962</t>
+          <t>3230; 14039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1919; 12740</t>
+          <t>1895; 12241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3184; 12770</t>
+          <t>3458; 13354</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>27691</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3093; 13032</t>
+          <t>2762; 12884</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2881; 14613</t>
+          <t>2917; 15795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1050; 8712</t>
+          <t>1044; 8542</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5569; 32427</t>
+          <t>5740; 35733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14087; 33439</t>
+          <t>14370; 33527</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3204; 16998</t>
+          <t>3916; 17870</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8029; 25022</t>
+          <t>7832; 25818</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7389; 18817</t>
+          <t>7331; 19449</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19098; 40789</t>
+          <t>19455; 42947</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8612; 26629</t>
+          <t>8742; 26782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10587; 29028</t>
+          <t>10080; 28237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16105; 45613</t>
+          <t>16307; 46108</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91099</t>
+          <t>100625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>175161</t>
+          <t>190748</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>53626; 87169</t>
+          <t>53124; 86689</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58372; 97334</t>
+          <t>58858; 95864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55427; 89460</t>
+          <t>53931; 87844</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69011; 117885</t>
+          <t>81127; 128731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56197; 89994</t>
+          <t>54411; 88664</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49713; 87651</t>
+          <t>51634; 88373</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44825; 77164</t>
+          <t>45734; 77020</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>64888; 102988</t>
+          <t>75134; 108407</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>116618; 164141</t>
+          <t>118756; 165226</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117455; 169864</t>
+          <t>118624; 171956</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107352; 156182</t>
+          <t>106669; 152636</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>144682; 207213</t>
+          <t>163280; 221072</t>
         </is>
       </c>
     </row>
